--- a/insurance_data/5_savings/legal/extracted_data.xlsx
+++ b/insurance_data/5_savings/legal/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT15"/>
+  <dimension ref="A1:AT16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1419,12 +1419,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>메리츠화재</t>
+          <t>카카오페이손해보험</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>(무) 메리츠 성공파트너 종합보험2601(1종)</t>
+          <t>(무)초중학생보험2604</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1434,34 +1434,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>민사소송법률비용Ⅱ</t>
+          <t>민사소송법률비용</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>피보험자에게 소송의 원인이 되는 사건이 발생하여, 소송사건이 보험기간 중에 대한민국 법원에 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료됨에 따라 피보험자가 법률비용을 부담하는 경우</t>
+          <t>소송제기의 원인이 되는 사건이 발생하고 대한민국 법원에 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료된 경우</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3천만원</t>
+          <t>변호사비용 : 1500만원까지, 인지액+송달료 : 500만원까지</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3천만원</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>10,432 원</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>9,672 원</t>
-        </is>
-      </c>
+          <t>변호사비용 : 1500만원까지, 인지액+송달료 : 500만원까지</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
@@ -1474,55 +1466,31 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>장기보장성 비교 공시 (7).xls</t>
+          <t>장기보장성 비교 공시 (11).xls</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>메리츠화재</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>(무) 메리츠 성공파트너 종합보험2601(1종)</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>민사소송법률비용Ⅱ</t>
+          <t>민사소송법률비용</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>피보험자에게 소송의 원인이 되는 사건이 발생하여, 소송사건이 보험기간 중에 대한민국 법원에 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료됨에 따라 피보험자가 법률비용을 부담하는 경우</t>
+          <t>소송제기의 원인이 되는 사건이 발생하고 대한민국 법원에 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료된 경우</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3천만원</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>10,432</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>9,672</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>98.9</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>108.5</t>
-        </is>
-      </c>
+          <t>변호사비용 : 1500만원까지, 인지액+송달료 : 500만원까지</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -1552,7 +1520,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>(무) 메리츠 성공파트너 종합보험2601(2종)</t>
+          <t>(무) 메리츠 성공파트너 종합보험2601(1종)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1613,7 +1581,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>(무) 메리츠 성공파트너 종합보험2601(2종)</t>
+          <t>(무) 메리츠 성공파트너 종합보험2601(1종)</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1675,12 +1643,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>하나손보</t>
+          <t>메리츠화재</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>무배당 하나더퍼스트 교직원 안심보험(2601)</t>
+          <t>(무) 메리츠 성공파트너 종합보험2601(2종)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1690,32 +1658,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>교원소청변호사비용손해</t>
+          <t>민사소송법률비용Ⅱ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>교원소청심사 청구의 원인이 되는 사건이 발생하여 교원소청 심사를 보험기간 중에 청구하고 대리인으로 변호사를 선임한 경우 그 소청이 처분 취소, 변경 등 심사 결정으로 종료됨에 따라 피보험자가 부담한 변호사선임비용</t>
+          <t>피보험자에게 소송의 원인이 되는 사건이 발생하여, 소송사건이 보험기간 중에 대한민국 법원에 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료됨에 따라 피보험자가 법률비용을 부담하는 경우</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>300만원 한도(자기부담금 10만원)</t>
+          <t>3천만원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>300만원 한도(자기부담금 10만원)</t>
+          <t>3천만원</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10,487 원</t>
+          <t>10,432 원</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>9,399 원</t>
+          <t>9,672 원</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1736,47 +1704,47 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>하나손보</t>
+          <t>메리츠화재</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>무배당 하나더퍼스트 교직원 안심보험(2601)</t>
+          <t>(무) 메리츠 성공파트너 종합보험2601(2종)</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>교원소청변호사비용손해</t>
+          <t>민사소송법률비용Ⅱ</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>교원소청심사 청구의 원인이 되는 사건이 발생하여 교원소청 심사를 보험기간 중에 청구하고 대리인으로 변호사를 선임한 경우 그 소청이 처분 취소, 변경 등 심사 결정으로 종료됨에 따라 피보험자가 부담한 변호사선임비용</t>
+          <t>피보험자에게 소송의 원인이 되는 사건이 발생하여, 소송사건이 보험기간 중에 대한민국 법원에 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료됨에 따라 피보험자가 법률비용을 부담하는 경우</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>300만원 한도(자기부담금 10만원)</t>
+          <t>3천만원</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>10,487</t>
+          <t>10,432</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>9,399</t>
+          <t>9,672</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>121.1</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr"/>
@@ -1808,7 +1776,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>무배당 하나더퍼스트 교직원 안심보험(2601)</t>
+          <t>무배당 하나더퍼스트 교직원 안심보험(2604)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1818,26 +1786,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>민사소송법률비용손해</t>
+          <t>교원소청변호사비용손해</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>피보험자에게 소송제기의 원인이 되는 사건이 발생하여, 약관에서 정한 민사소송 사건이 보험기간 중에 대한민국 법원에 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료됨에 따라 피보험자가 부담한 법률비용※ 연간 하나의 사건에 의해 제기된 소송에 한함</t>
+          <t>교원소청심사 청구의 원인이 되는 사건이 발생하여 교원소청 심사를 보험기간 중에 청구하고 대리인으로 변호사를 선임한 경우 그 소청이 처분 취소, 변경 등 심사 결정으로 종료됨에 따라 피보험자가 부담한 변호사선임비용</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>· 변호사비용『변호사보수의 소송비용산입에 관한 규칙』에 정한 변호사비용의 한도 내에서 실제 부담한 변호사 보수액 중 자기부담금 10만원을 초과하는 금액· 인지액+송달료 500만원 한도</t>
+          <t>300만원 한도(자기부담금 10만원)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>· 변호사비용『변호사보수의 소송비용산입에 관한 규칙』에 정한 변호사비용의 한도 내에서 실제 부담한 변호사 보수액 중 자기부담금 10만원을 초과하는 금액· 인지액+송달료 500만원 한도</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+          <t>300만원 한도(자기부담금 10만원)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>10,651 원</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>9,551 원</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
@@ -1854,27 +1830,51 @@
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>하나손보</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>무배당 하나더퍼스트 교직원 안심보험(2604)</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>민사소송법률비용손해</t>
+          <t>교원소청변호사비용손해</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>피보험자에게 소송제기의 원인이 되는 사건이 발생하여, 약관에서 정한 민사소송 사건이 보험기간 중에 대한민국 법원에 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료됨에 따라 피보험자가 부담한 법률비용※ 연간 하나의 사건에 의해 제기된 소송에 한함</t>
+          <t>교원소청심사 청구의 원인이 되는 사건이 발생하여 교원소청 심사를 보험기간 중에 청구하고 대리인으로 변호사를 선임한 경우 그 소청이 처분 취소, 변경 등 심사 결정으로 종료됨에 따라 피보험자가 부담한 변호사선임비용</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>· 변호사비용『변호사보수의 소송비용산입에 관한 규칙』에 정한 변호사비용의 한도 내에서 실제 부담한 변호사 보수액 중 자기부담금 10만원을 초과하는 금액· 인지액+송달료 500만원 한도</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>300만원 한도(자기부담금 10만원)</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>10,651</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>9,551</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>121.2</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>119.5</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>무배당 하나더퍼스트 교직원 안심보험(2601)</t>
+          <t>무배당 하나더퍼스트 교직원 안심보험(2604)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>행정소송법률비용손해</t>
+          <t>민사소송법률비용손해</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>피보험자에게 소송제기의 원인이 되는 사건이 발생하여, 약관에서 정한 행정소송 사건이 보험기간 중에 대한민국 법원에 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료됨에 따라 피보험자가 부담한 법률비용</t>
+          <t>피보험자에게 소송제기의 원인이 되는 사건이 발생하여, 약관에서 정한 민사소송 사건이 보험기간 중에 대한민국 법원에 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료됨에 따라 피보험자가 부담한 법률비용※ 연간 하나의 사건에 의해 제기된 소송에 한함</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1954,12 +1954,12 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>행정소송법률비용손해</t>
+          <t>민사소송법률비용손해</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>피보험자에게 소송제기의 원인이 되는 사건이 발생하여, 약관에서 정한 행정소송 사건이 보험기간 중에 대한민국 법원에 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료됨에 따라 피보험자가 부담한 법률비용</t>
+          <t>피보험자에게 소송제기의 원인이 되는 사건이 발생하여, 약관에서 정한 민사소송 사건이 보험기간 중에 대한민국 법원에 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료됨에 따라 피보험자가 부담한 법률비용※ 연간 하나의 사건에 의해 제기된 소송에 한함</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1995,12 +1995,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>라이나손보(에이스손보)</t>
+          <t>하나손보</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>(무)무심사 시니어안심보험2404 1종 무심사형</t>
+          <t>무배당 하나더퍼스트 교직원 안심보험(2604)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2010,22 +2010,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>민사소송법률비용보장 특별약관</t>
+          <t>행정소송법률비용손해</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>보험기간 중에 피보험자에게 소송제기의 원인이 되는 사건이 발생하여, 민사1심 합의/단독사건과 민사 소액/항소/상고사건이 보험기간 중에 대한민국 법원에서 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료됨에 따라 피보험자가 부담하는 경우</t>
+          <t>피보험자에게 소송제기의 원인이 되는 사건이 발생하여, 약관에서 정한 행정소송 사건이 보험기간 중에 대한민국 법원에 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료됨에 따라 피보험자가 부담한 법률비용</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>변호사비용: 1,500만원한도  (1사고당 자기부담금 10만원)-. 인지액+송달료 : 500만원 한도</t>
+          <t>· 변호사비용『변호사보수의 소송비용산입에 관한 규칙』에 정한 변호사비용의 한도 내에서 실제 부담한 변호사 보수액 중 자기부담금 10만원을 초과하는 금액· 인지액+송달료 500만원 한도</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>변호사비용: 1,500만원한도  (1사고당 자기부담금 10만원)-. 인지액+송달료 : 500만원 한도</t>
+          <t>· 변호사비용『변호사보수의 소송비용산입에 관한 규칙』에 정한 변호사비용의 한도 내에서 실제 부담한 변호사 보수액 중 자기부담금 10만원을 초과하는 금액· 인지액+송달료 500만원 한도</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2050,17 +2050,17 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>민사소송법률비용보장 특별약관</t>
+          <t>행정소송법률비용손해</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>보험기간 중에 피보험자에게 소송제기의 원인이 되는 사건이 발생하여, 민사1심 합의/단독사건과 민사 소액/항소/상고사건이 보험기간 중에 대한민국 법원에서 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료됨에 따라 피보험자가 부담하는 경우</t>
+          <t>피보험자에게 소송제기의 원인이 되는 사건이 발생하여, 약관에서 정한 행정소송 사건이 보험기간 중에 대한민국 법원에 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료됨에 따라 피보험자가 부담한 법률비용</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>변호사비용: 1,500만원한도  (1사고당 자기부담금 10만원)-. 인지액+송달료 : 500만원 한도</t>
+          <t>· 변호사비용『변호사보수의 소송비용산입에 관한 규칙』에 정한 변호사비용의 한도 내에서 실제 부담한 변호사 보수액 중 자기부담금 10만원을 초과하는 금액· 인지액+송달료 500만원 한도</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>(무)무심사 시니어안심보험2404 2종 일반심사형</t>
+          <t>(무)무심사 시니어안심보험2404 1종 무심사형</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2184,6 +2184,102 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>라이나손보(에이스손보)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>(무)무심사 시니어안심보험2404 2종 일반심사형</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>특약</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>민사소송법률비용보장 특별약관</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>보험기간 중에 피보험자에게 소송제기의 원인이 되는 사건이 발생하여, 민사1심 합의/단독사건과 민사 소액/항소/상고사건이 보험기간 중에 대한민국 법원에서 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료됨에 따라 피보험자가 부담하는 경우</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>변호사비용: 1,500만원한도  (1사고당 자기부담금 10만원)-. 인지액+송달료 : 500만원 한도</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>변호사비용: 1,500만원한도  (1사고당 자기부담금 10만원)-. 인지액+송달료 : 500만원 한도</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>장기보장성 비교 공시 (7).xls</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>민사소송법률비용보장 특별약관</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>보험기간 중에 피보험자에게 소송제기의 원인이 되는 사건이 발생하여, 민사1심 합의/단독사건과 민사 소액/항소/상고사건이 보험기간 중에 대한민국 법원에서 제기되어 그 소송이 판결, 소송상 조정 또는 소송상 화해로 종료됨에 따라 피보험자가 부담하는 경우</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>변호사비용: 1,500만원한도  (1사고당 자기부담금 10만원)-. 인지액+송달료 : 500만원 한도</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/insurance_data/5_savings/legal/extracted_data.xlsx
+++ b/insurance_data/5_savings/legal/extracted_data.xlsx
@@ -912,7 +912,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>무배당 하나더퍼스트 교직원 안심보험(2601)</t>
+          <t>무배당 하나더퍼스트 교직원 안심보험(2604)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10,487 원</t>
+          <t>10,651 원</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9,399 원</t>
+          <t>9,551 원</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -973,7 +973,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>무배당 하나더퍼스트 교직원 안심보험(2601)</t>
+          <t>무배당 하나더퍼스트 교직원 안심보험(2604)</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>10,487</t>
+          <t>10,651</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>9,399</t>
+          <t>9,551</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>121.1</t>
+          <t>121.2</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>무배당 하나더퍼스트 교직원 안심보험(2601)</t>
+          <t>무배당 하나더퍼스트 교직원 안심보험(2604)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>무배당 하나더퍼스트 교직원 안심보험(2601)</t>
+          <t>무배당 하나더퍼스트 교직원 안심보험(2604)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
